--- a/diseases/d052/2005-2009.xlsx
+++ b/diseases/d052/2005-2009.xlsx
@@ -10681,9 +10681,6 @@
       <c r="O69" t="n">
         <v>3</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.0561918081147152</v>
       </c>
@@ -11373,9 +11370,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -12065,9 +12059,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12905,9 +12896,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13745,9 +13733,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -14437,9 +14422,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -15275,9 +15257,6 @@
         <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">

--- a/diseases/d052/2005-2009.xlsx
+++ b/diseases/d052/2005-2009.xlsx
@@ -6345,12 +6345,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6375,93 +6375,104 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>0.001592859148721914</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_CHIK_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_CHIK_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6488,17 +6499,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6523,12 +6534,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6537,79 +6548,165 @@
       <c r="O41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.004331584715899372</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_CHIK_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_CHIK_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Chikungunya virus disease</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>1</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_CHIK_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6671,12 +6768,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6789,12 +6886,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6819,25 +6916,25 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.009358656641580086</v>
+        <v>0.004331584715899372</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -6870,42 +6967,42 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6937,12 +7034,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6967,25 +7064,25 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.004331584715899372</v>
+        <v>0</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -7018,42 +7115,42 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7115,25 +7212,25 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0.004679328320790043</v>
+        <v>0.009358656641580086</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -7233,12 +7330,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7263,25 +7360,25 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.004331584715899372</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7314,42 +7411,42 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7411,12 +7508,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7529,12 +7626,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7559,25 +7656,25 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.004331584715899372</v>
+        <v>0</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -7610,42 +7707,42 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7707,12 +7804,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7825,12 +7922,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7855,12 +7952,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -7873,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.004679328320790043</v>
+        <v>0.004331584715899372</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -7906,42 +8003,42 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8003,12 +8100,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8121,12 +8218,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8151,25 +8248,25 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.008663169431798744</v>
+        <v>0.004679328320790043</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -8202,42 +8299,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8299,25 +8396,25 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.01403798496237013</v>
+        <v>0.004679328320790043</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8447,25 +8544,25 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.004331584715899372</v>
+        <v>0.008663169431798744</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -8595,25 +8692,25 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.009358656641580086</v>
+        <v>0.01403798496237013</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -8743,25 +8840,25 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01299475414769812</v>
+        <v>0.004331584715899372</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -8891,25 +8988,25 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0.02295366788365483</v>
+        <v>0.009358656641580086</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -9039,25 +9136,25 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.004316976410443612</v>
+        <v>0.01299475414769812</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -9187,25 +9284,25 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.004590733576730967</v>
+        <v>0.02295366788365483</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -9305,12 +9402,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9335,93 +9432,104 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O60" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R60" t="n">
-        <v>0.009181467153461935</v>
+        <v>0.02060010874005092</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_CHIK_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_CHIK_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9448,17 +9556,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9483,93 +9591,179 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N61" t="n">
+        <v>13</v>
+      </c>
+      <c r="O61" t="n">
+        <v>13</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_CHIK_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_CHIK_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Chikungunya virus disease</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN61" t="b">
         <v>1</v>
       </c>
-      <c r="O61" t="n">
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_CHIK_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT61" t="n">
         <v>1</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.01415535058450628</v>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP61" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="n">
-        <v>0</v>
-      </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9601,12 +9795,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9631,25 +9825,25 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.009181467153461935</v>
+        <v>0.004316976410443612</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -9682,42 +9876,42 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9749,12 +9943,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9779,25 +9973,25 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>0.004590733576730967</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -9830,42 +10024,42 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9897,12 +10091,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9927,12 +10121,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -9945,7 +10139,7 @@
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.008633952820887223</v>
+        <v>0.009181467153461935</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -9978,42 +10172,42 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10045,12 +10239,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10075,25 +10269,25 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0137722007301929</v>
+        <v>0.01415535058450628</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -10126,42 +10320,42 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10193,12 +10387,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10223,25 +10417,25 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>0.009181467153461935</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -10274,42 +10468,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10341,12 +10535,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10371,25 +10565,25 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0.004316976410443612</v>
+        <v>0</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -10422,17 +10616,17 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -10442,17 +10636,17 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
@@ -10489,12 +10683,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10519,25 +10713,25 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>0.004590733576730967</v>
+        <v>0.008633952820887223</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -10570,42 +10764,42 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10637,12 +10831,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10667,12 +10861,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -10681,90 +10875,79 @@
       <c r="O69" t="n">
         <v>3</v>
       </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
       <c r="R69" t="n">
-        <v>0.0561918081147152</v>
+        <v>0.0137722007301929</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10791,17 +10974,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10826,179 +11009,93 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3</v>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG70" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN70" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11030,12 +11127,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -11060,25 +11157,25 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>0.004316976410443612</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -11111,17 +11208,17 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -11131,17 +11228,17 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
@@ -11208,25 +11305,25 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.0137722007301929</v>
+        <v>0.004590733576730967</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -11356,22 +11453,22 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>0.0561918081147152</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -11515,19 +11612,19 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -11749,12 +11846,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -11897,25 +11994,25 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>0.0137722007301929</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -12045,12 +12142,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -12204,12 +12301,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -12438,12 +12535,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12556,12 +12653,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12595,16 +12692,16 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>0.004316976410443612</v>
+        <v>0</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -12637,42 +12734,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12704,12 +12801,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12734,93 +12831,104 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
         <v>1</v>
       </c>
-      <c r="O81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0.004590733576730967</v>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP81" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
-      <c r="AT81" t="n">
-        <v>0</v>
-      </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12847,7 +12955,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -12882,12 +12990,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -12896,23 +13004,98 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN82" t="b">
+        <v>1</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -13006,17 +13189,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -13041,12 +13224,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -13055,165 +13238,79 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD83" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF83" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG83" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN83" t="b">
-        <v>1</v>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13245,12 +13342,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -13275,25 +13372,25 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>0.004316976410443612</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -13326,17 +13423,17 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -13346,17 +13443,17 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
@@ -13393,12 +13490,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -13441,7 +13538,7 @@
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.004316976410443612</v>
+        <v>0.004590733576730967</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -13474,42 +13571,42 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13541,12 +13638,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13571,93 +13668,104 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.009181467153461935</v>
+        <v>0</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13792,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -13719,12 +13827,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -13733,23 +13841,98 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN87" t="b">
+        <v>1</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -13843,17 +14026,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13878,12 +14061,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -13892,165 +14075,79 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD88" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF88" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG88" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN88" t="b">
-        <v>1</v>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14082,12 +14179,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -14112,25 +14209,25 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>0.004316976410443612</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -14163,17 +14260,17 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -14183,17 +14280,17 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
@@ -14260,25 +14357,25 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0.004590733576730967</v>
+        <v>0.009181467153461935</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -14408,12 +14505,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -14567,12 +14664,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -14801,12 +14898,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -14919,12 +15016,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14967,7 +15064,7 @@
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.004316976410443612</v>
+        <v>0.004590733576730967</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -15000,42 +15097,42 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15067,12 +15164,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -15097,93 +15194,104 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-11-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.01836293430692387</v>
+        <v>0</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15210,7 +15318,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -15245,12 +15353,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-11-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -15259,23 +15367,98 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN96" t="b">
+        <v>1</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -15369,17 +15552,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -15404,12 +15587,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-11-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -15418,165 +15601,79 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD97" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE97" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF97" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG97" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN97" t="b">
-        <v>1</v>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15608,12 +15705,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -15638,25 +15735,25 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-11-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>0.004316976410443612</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -15689,17 +15786,17 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -15709,17 +15806,17 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
@@ -15756,12 +15853,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -15795,16 +15892,16 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.008633952820887223</v>
+        <v>0.01836293430692387</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -15837,40 +15934,729 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>2</v>
+      </c>
+      <c r="O103" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.008633952820887223</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="AW99" t="inlineStr">
+      <c r="AW103" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
+      <c r="AX103" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="AY99" t="inlineStr">
+      <c r="AY103" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
+      <c r="AZ103" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="BA99" t="inlineStr">
+      <c r="BA103" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="BB99" t="inlineStr">
+      <c r="BB103" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="BC99" t="inlineStr">
+      <c r="BC103" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -15992,7 +16778,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -16002,7 +16788,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -16022,7 +16808,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -16032,7 +16818,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -16054,7 +16840,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
